--- a/programs/2026-10_India_Pilot/program.xlsx
+++ b/programs/2026-10_India_Pilot/program.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Authentica\Presales\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/20baf977624bf256/Documents/GitHub/MondayProgramSync/MondayProgramSync/programs/2026-10_India_Pilot/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE653987-1F5E-43B0-B2D1-4B533E2FA222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{BE653987-1F5E-43B0-B2D1-4B533E2FA222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23D0329B-1208-410C-8A43-6BC97C423E91}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1066,7 +1066,7 @@
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="21" style="5" customWidth="1"/>
-    <col min="2" max="2" width="71.25" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="54.625" style="5" customWidth="1"/>
     <col min="3" max="3" width="24.875" style="5" customWidth="1"/>
     <col min="4" max="5" width="34" style="5" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="8.75" style="5"/>
@@ -1180,7 +1180,7 @@
         <v>37</v>
       </c>
       <c r="C10" s="21">
-        <v>45901</v>
+        <v>46101</v>
       </c>
       <c r="D10" s="38" t="s">
         <v>40</v>
@@ -1208,7 +1208,7 @@
         <v>27</v>
       </c>
       <c r="C12" s="21">
-        <v>45992</v>
+        <v>46130</v>
       </c>
       <c r="D12" s="38" t="s">
         <v>41</v>

--- a/programs/2026-10_India_Pilot/program.xlsx
+++ b/programs/2026-10_India_Pilot/program.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/20baf977624bf256/Documents/GitHub/MondayProgramSync/MondayProgramSync/programs/2026-10_India_Pilot/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{BE653987-1F5E-43B0-B2D1-4B533E2FA222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23D0329B-1208-410C-8A43-6BC97C423E91}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{BE653987-1F5E-43B0-B2D1-4B533E2FA222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C2E96C1-FC9B-4774-9B18-A8F287792B8B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1123,7 +1123,7 @@
         <v>16</v>
       </c>
       <c r="C6" s="21">
-        <v>45870</v>
+        <v>46024</v>
       </c>
       <c r="D6" s="38" t="s">
         <v>39</v>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="C8" s="21">
         <f>$C$6+14</f>
-        <v>45884</v>
+        <v>46038</v>
       </c>
       <c r="D8" s="40" t="s">
         <v>38</v>
@@ -1225,7 +1225,7 @@
         <v>43</v>
       </c>
       <c r="C13" s="21">
-        <v>46003</v>
+        <v>46234</v>
       </c>
       <c r="D13" s="38" t="s">
         <v>44</v>
